--- a/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-Hauptversicherter.xlsx
+++ b/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-Hauptversicherter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:43:28+00:00</t>
+    <t>2025-02-07T07:29:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1138,7 +1138,7 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://example.org/ValueSet/moped-related-person-relationship-type</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1174,7 +1174,7 @@
     <t>RelatedPerson.relationship.coding.code</t>
   </si>
   <si>
-    <t>GUAR</t>
+    <t>SELF</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.display</t>
@@ -1764,7 +1764,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="60.62109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.61328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
